--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122115625</v>
+        <v>122114966</v>
       </c>
       <c r="B2" t="n">
-        <v>94912</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Mol, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332960</v>
+        <v>332966</v>
       </c>
       <c r="R2" t="n">
-        <v>6422461</v>
+        <v>6422326</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observerad och hörd. Fanns även spår från födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +786,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122114966</v>
+        <v>122115625</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
+        <v>94921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,53 +816,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mol, Vg</t>
+          <t>Nol, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332966</v>
+        <v>332960</v>
       </c>
       <c r="R3" t="n">
-        <v>6422326</v>
+        <v>6422461</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Observerad och hörd. Fanns även spår från födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122115625</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122115625</v>
+        <v>122114966</v>
       </c>
       <c r="B2" t="n">
-        <v>94957</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Mol, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332960</v>
+        <v>332966</v>
       </c>
       <c r="R2" t="n">
-        <v>6422461</v>
+        <v>6422326</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observerad och hörd. Fanns även spår från födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +786,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122114966</v>
+        <v>122115625</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>94969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,53 +816,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mol, Vg</t>
+          <t>Nol, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332966</v>
+        <v>332960</v>
       </c>
       <c r="R3" t="n">
-        <v>6422326</v>
+        <v>6422461</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Observerad och hörd. Fanns även spår från födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>122115625</v>
       </c>
       <c r="B3" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -807,7 +802,7 @@
         <v>122115625</v>
       </c>
       <c r="B3" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,11 +816,6 @@
       </c>
       <c r="E3" t="n">
         <v>2180</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122114966</v>
+        <v>122115625</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>94996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mol, Vg</t>
+          <t>Nol, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332966</v>
+        <v>332960</v>
       </c>
       <c r="R2" t="n">
-        <v>6422326</v>
+        <v>6422461</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Observerad och hörd. Fanns även spår från födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122115625</v>
+        <v>122114966</v>
       </c>
       <c r="B3" t="n">
-        <v>94983</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,40 +804,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Mol, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332960</v>
+        <v>332966</v>
       </c>
       <c r="R3" t="n">
-        <v>6422461</v>
+        <v>6422326</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observerad och hörd. Fanns även spår från födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>122114966</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>122114966</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122115625</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,11 +790,11 @@
         <v>122114966</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 380-2025 artfynd.xlsx
+++ b/artfynd/A 380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122115625</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,8 +918,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122114966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>